--- a/data/trans_bre/P16A_n_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,78</t>
+          <t>5,59; 11,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 15,26</t>
+          <t>6,61; 14,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,99</t>
+          <t>3,34; 10,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 12,6</t>
+          <t>-1,8; 12,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>139,62; 723,22</t>
+          <t>164,43; 719,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,94; 405,05</t>
+          <t>88,49; 388,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,83; 429,22</t>
+          <t>52,88; 405,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 257,22</t>
+          <t>-19,71; 250,99</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 13,55</t>
+          <t>7,47; 13,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 14,66</t>
+          <t>6,6; 14,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 11,05</t>
+          <t>3,37; 10,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 10,02</t>
+          <t>-4,12; 10,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>159,21; 505,7</t>
+          <t>144,93; 478,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,04; 178,66</t>
+          <t>58,56; 187,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,84; 177,77</t>
+          <t>32,88; 172,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 105,17</t>
+          <t>-25,43; 103,1</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,91</t>
+          <t>2,47; 9,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 15,95</t>
+          <t>7,08; 15,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 11,37</t>
+          <t>3,39; 11,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,57</t>
+          <t>-0,58; 10,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,82; 146,52</t>
+          <t>22,87; 134,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,78; 149,91</t>
+          <t>46,16; 150,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,41; 139,08</t>
+          <t>27,39; 130,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 85,84</t>
+          <t>-3,06; 82,62</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 12,72</t>
+          <t>2,92; 12,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 20,4</t>
+          <t>10,05; 20,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,0</t>
+          <t>3,45; 13,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 25,52</t>
+          <t>4,8; 26,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,93; 96,92</t>
+          <t>16,24; 100,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,58; 134,82</t>
+          <t>47,85; 133,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 77,14</t>
+          <t>16,58; 79,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,03; 294,18</t>
+          <t>18,12; 256,4</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 17,43</t>
+          <t>3,24; 17,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 22,55</t>
+          <t>9,0; 22,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,24; 25,23</t>
+          <t>10,87; 24,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 14,88</t>
+          <t>3,93; 14,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 57,52</t>
+          <t>9,07; 54,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,56; 61,67</t>
+          <t>20,1; 60,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,98; 80,62</t>
+          <t>29,09; 78,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 37,74</t>
+          <t>8,53; 38,63</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,09; 27,7</t>
+          <t>13,45; 28,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 14,78</t>
+          <t>-0,73; 14,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,04; 19,1</t>
+          <t>4,62; 19,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,67; 39,86</t>
+          <t>11,58; 39,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,59; 70,71</t>
+          <t>27,52; 71,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 24,18</t>
+          <t>-0,97; 23,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,96; 39,43</t>
+          <t>8,23; 40,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,52; 79,04</t>
+          <t>21,33; 78,53</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 15,22</t>
+          <t>-0,36; 15,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 14,18</t>
+          <t>2,01; 14,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 13,32</t>
+          <t>-0,42; 12,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 17,98</t>
+          <t>7,46; 18,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 24,98</t>
+          <t>-0,45; 26,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 19,01</t>
+          <t>2,43; 19,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 19,67</t>
+          <t>-0,7; 18,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,03; 28,06</t>
+          <t>10,37; 28,29</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,13; 14,29</t>
+          <t>10,28; 14,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,36; 17,04</t>
+          <t>12,7; 17,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,15</t>
+          <t>9,81; 14,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,26; 25,61</t>
+          <t>9,57; 26,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,07; 87,17</t>
+          <t>55,17; 85,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,57; 70,25</t>
+          <t>47,83; 70,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,84; 64,91</t>
+          <t>40,75; 65,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,04; 102,23</t>
+          <t>32,27; 106,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 11,67</t>
+          <t>5,44; 11,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 14,74</t>
+          <t>6,87; 14,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,72</t>
+          <t>3,54; 11,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 12,18</t>
+          <t>-1,69; 12,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>164,43; 719,85</t>
+          <t>148,07; 777,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,49; 388,54</t>
+          <t>102,1; 398,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,88; 405,28</t>
+          <t>59,04; 435,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 250,99</t>
+          <t>-16,96; 210,38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,29</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 13,73</t>
+          <t>7,02; 13,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 14,98</t>
+          <t>6,48; 14,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 10,73</t>
+          <t>3,31; 10,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 10,01</t>
+          <t>-0,34; 10,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>144,93; 478,34</t>
+          <t>154,35; 457,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,56; 187,18</t>
+          <t>53,22; 180,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,88; 172,41</t>
+          <t>32,42; 164,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 103,1</t>
+          <t>-3,9; 110,62</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,02</t>
+          <t>7,88</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,4</t>
+          <t>2,51; 9,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 15,9</t>
+          <t>7,01; 15,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,05</t>
+          <t>3,55; 10,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 10,23</t>
+          <t>4,07; 12,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,87; 134,13</t>
+          <t>24,49; 135,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,16; 150,04</t>
+          <t>44,36; 144,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,39; 130,21</t>
+          <t>27,44; 122,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 82,62</t>
+          <t>24,03; 103,89</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,67</t>
+          <t>7,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 12,99</t>
+          <t>3,48; 13,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 20,39</t>
+          <t>10,17; 20,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 13,24</t>
+          <t>2,95; 12,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 26,27</t>
+          <t>2,32; 11,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,24; 100,36</t>
+          <t>18,32; 102,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,85; 133,51</t>
+          <t>49,26; 135,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,58; 79,6</t>
+          <t>12,77; 75,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 256,4</t>
+          <t>7,73; 47,03</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,51</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 17,09</t>
+          <t>3,07; 16,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 22,38</t>
+          <t>8,69; 23,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,87; 24,43</t>
+          <t>10,54; 24,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 14,9</t>
+          <t>5,27; 15,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 54,78</t>
+          <t>8,26; 53,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,1; 60,74</t>
+          <t>19,46; 63,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,09; 78,71</t>
+          <t>27,3; 77,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 38,63</t>
+          <t>11,47; 40,37</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,67</t>
+          <t>14,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,45; 28,39</t>
+          <t>13,55; 28,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 14,66</t>
+          <t>-0,53; 14,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,62; 19,42</t>
+          <t>5,03; 19,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,58; 39,14</t>
+          <t>9,26; 19,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,52; 71,94</t>
+          <t>27,7; 71,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 23,82</t>
+          <t>-0,57; 23,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 40,37</t>
+          <t>9,23; 40,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,33; 78,53</t>
+          <t>16,68; 40,41</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,73</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 15,58</t>
+          <t>-1,64; 15,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 14,52</t>
+          <t>1,74; 14,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 12,56</t>
+          <t>-0,87; 12,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 18,05</t>
+          <t>7,5; 18,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 26,42</t>
+          <t>-2,33; 25,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 19,39</t>
+          <t>2,06; 19,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 18,47</t>
+          <t>-1,16; 19,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 28,29</t>
+          <t>10,77; 28,68</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>10,82</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,27</t>
+          <t>10,24; 14,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,7; 17,22</t>
+          <t>12,46; 17,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,81; 14,21</t>
+          <t>9,57; 13,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,57; 26,2</t>
+          <t>8,66; 12,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,17; 85,78</t>
+          <t>56,14; 86,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,83; 70,69</t>
+          <t>47,26; 70,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,75; 65,39</t>
+          <t>39,75; 63,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,27; 106,48</t>
+          <t>27,89; 45,39</t>
         </is>
       </c>
     </row>
